--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -786,7 +786,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G30" s="2"/>
     </row>
@@ -1478,10 +1478,10 @@
         <v>0.19</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="48">
@@ -1869,10 +1869,10 @@
         <v>0.69</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="65">
@@ -2191,10 +2191,10 @@
         <v>-0.09</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="79">
@@ -2214,10 +2214,10 @@
         <v>-0.06</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="80">
@@ -2237,10 +2237,10 @@
         <v>-0.06</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="81">
@@ -2257,13 +2257,13 @@
         <v>21</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="82">
@@ -2306,10 +2306,10 @@
         <v>-0.53</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.72</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.4</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="84">
@@ -2329,10 +2329,10 @@
         <v>0.63</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.82</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="85">
@@ -2352,10 +2352,10 @@
         <v>0.16</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="86">
@@ -2582,10 +2582,10 @@
         <v>0.19</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="96">
@@ -2605,10 +2605,10 @@
         <v>0.12</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="97">
@@ -2628,10 +2628,10 @@
         <v>0.15</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="98">
@@ -2648,13 +2648,13 @@
         <v>21</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="99">
@@ -2697,10 +2697,10 @@
         <v>-0.46</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>-0.57</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="101">
@@ -2720,10 +2720,10 @@
         <v>0.38</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="102">
@@ -2973,10 +2973,10 @@
         <v>0.18</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="113">
@@ -2996,10 +2996,10 @@
         <v>-0.5</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="114">
@@ -3019,10 +3019,10 @@
         <v>0.41</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="115">
@@ -3039,10 +3039,10 @@
         <v>21</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0.41</v>
@@ -3088,10 +3088,10 @@
         <v>-0.69</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="118">
@@ -3111,10 +3111,10 @@
         <v>-0.34</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="119">
@@ -3137,7 +3137,7 @@
         <v>-0.11</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="120">
@@ -3364,10 +3364,10 @@
         <v>-0.03</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="130">
@@ -3387,10 +3387,10 @@
         <v>-0.66</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="131">
@@ -3413,7 +3413,7 @@
         <v>-0.22</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="132">
@@ -3430,10 +3430,10 @@
         <v>21</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="G132" s="2" t="n">
         <v>0.5</v>
@@ -3479,10 +3479,10 @@
         <v>-0.8</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>-0.65</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="135">
@@ -3502,10 +3502,10 @@
         <v>-0.24</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="136">
@@ -3525,10 +3525,10 @@
         <v>-0.65</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="137">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
